--- a/static/data/exports/Retro_UK_GE_2009.xlsx
+++ b/static/data/exports/Retro_UK_GE_2009.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="Q3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>6</v>
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="Q21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>6</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Q39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>6</v>
@@ -8017,7 +8017,7 @@
         </is>
       </c>
       <c r="Q122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" t="n">
         <v>6</v>
@@ -10683,7 +10683,7 @@
         </is>
       </c>
       <c r="Q165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R165" t="n">
         <v>6</v>
@@ -11861,7 +11861,7 @@
         </is>
       </c>
       <c r="Q184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R184" t="n">
         <v>6</v>
@@ -12187,11 +12187,11 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>1487680</v>
+        <v>1487681</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Vijay Nath</t>
+          <t>Harish Walia</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Vijay Nath</t>
+          <t>Harish Walia</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12249,11 +12249,11 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1487681</v>
+        <v>1487680</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Harish Walia</t>
+          <t>Vijay Nath</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Harish Walia</t>
+          <t>Vijay Nath</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12977,7 +12977,7 @@
         </is>
       </c>
       <c r="Q202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R202" t="n">
         <v>6</v>
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="Q219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R219" t="n">
         <v>6</v>
@@ -15147,7 +15147,7 @@
         </is>
       </c>
       <c r="Q237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R237" t="n">
         <v>6</v>
@@ -15845,20 +15845,20 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1487922</v>
+        <v>1487923</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Dr. Nagendra Dutt Jagoodi</t>
+          <t>Anjana Walia</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RJSD</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>16059</v>
+        <v>16067</v>
       </c>
       <c r="E249" t="n">
         <v>91</v>
@@ -15882,12 +15882,12 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Dr. Nagendra Dutt Jagoodi</t>
+          <t>Anjana Walia</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RJSD</t>
         </is>
       </c>
       <c r="Q249" t="b">
@@ -15907,20 +15907,20 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1487923</v>
+        <v>1487922</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Anjana Walia</t>
+          <t>Dr. Nagendra Dutt Jagoodi</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>RJSD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>16067</v>
+        <v>16059</v>
       </c>
       <c r="E250" t="n">
         <v>91</v>
@@ -15944,12 +15944,12 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Anjana Walia</t>
+          <t>Dr. Nagendra Dutt Jagoodi</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>RJSD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q250" t="b">
@@ -16263,7 +16263,7 @@
         </is>
       </c>
       <c r="Q255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R255" t="n">
         <v>6</v>
@@ -16651,11 +16651,11 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1488011</v>
+        <v>1488010</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Harish Walia</t>
+          <t>Barhm Dev Jha</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Harish Walia</t>
+          <t>Barhm Dev Jha</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -16713,11 +16713,11 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1488010</v>
+        <v>1488011</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Barhm Dev Jha</t>
+          <t>Harish Walia</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Barhm Dev Jha</t>
+          <t>Harish Walia</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -17147,20 +17147,20 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1488019</v>
+        <v>1488018</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Sunder Lal Thapliyal</t>
+          <t>Bano Rani</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>VVS</t>
+          <t>NLHP</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>16069</v>
+        <v>16071</v>
       </c>
       <c r="E270" t="n">
         <v>85</v>
@@ -17184,12 +17184,12 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Sunder Lal Thapliyal</t>
+          <t>Bano Rani</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>VVS</t>
+          <t>NLHP</t>
         </is>
       </c>
       <c r="Q270" t="b">
@@ -17209,20 +17209,20 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1488018</v>
+        <v>1488019</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Bano Rani</t>
+          <t>Sunder Lal Thapliyal</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>NLHP</t>
+          <t>VVS</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>16071</v>
+        <v>16069</v>
       </c>
       <c r="E271" t="n">
         <v>85</v>
@@ -17246,12 +17246,12 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Bano Rani</t>
+          <t>Sunder Lal Thapliyal</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>NLHP</t>
+          <t>VVS</t>
         </is>
       </c>
       <c r="Q271" t="b">
@@ -18681,7 +18681,7 @@
         </is>
       </c>
       <c r="Q294" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R294" t="n">
         <v>6</v>
@@ -19797,7 +19797,7 @@
         </is>
       </c>
       <c r="Q312" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R312" t="n">
         <v>6</v>
@@ -20495,20 +20495,20 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>1488345</v>
+        <v>1488346</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Dr. Nagendra Dutt Jagoodi</t>
+          <t>Anjana Walia</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RJSD</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>16059</v>
+        <v>16067</v>
       </c>
       <c r="E324" t="n">
         <v>43</v>
@@ -20532,12 +20532,12 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Dr. Nagendra Dutt Jagoodi</t>
+          <t>Anjana Walia</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RJSD</t>
         </is>
       </c>
       <c r="Q324" t="b">
@@ -20557,20 +20557,20 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>1488346</v>
+        <v>1488345</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Anjana Walia</t>
+          <t>Dr. Nagendra Dutt Jagoodi</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>RJSD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>16067</v>
+        <v>16059</v>
       </c>
       <c r="E325" t="n">
         <v>43</v>
@@ -20594,12 +20594,12 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Anjana Walia</t>
+          <t>Dr. Nagendra Dutt Jagoodi</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>RJSD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q325" t="b">
@@ -20913,7 +20913,7 @@
         </is>
       </c>
       <c r="Q330" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R330" t="n">
         <v>6</v>
@@ -21301,11 +21301,11 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>1488420</v>
+        <v>1488419</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Barhm Dev Jha</t>
+          <t>Harish Walia</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Barhm Dev Jha</t>
+          <t>Harish Walia</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -21363,11 +21363,11 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>1488419</v>
+        <v>1488420</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Harish Walia</t>
+          <t>Barhm Dev Jha</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21400,7 +21400,7 @@
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Harish Walia</t>
+          <t>Barhm Dev Jha</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -22029,7 +22029,7 @@
         </is>
       </c>
       <c r="Q348" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R348" t="n">
         <v>6</v>
@@ -24277,20 +24277,20 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>1488610</v>
+        <v>1488609</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Subhash</t>
+          <t>Riasat Ali</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>MKD</t>
+          <t>RPI(A)</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>16105</v>
+        <v>16115</v>
       </c>
       <c r="E385" t="n">
         <v>44</v>
@@ -24314,12 +24314,12 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Subhash</t>
+          <t>Riasat Ali</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>MKD</t>
+          <t>RPI(A)</t>
         </is>
       </c>
       <c r="Q385" t="b">
@@ -24339,20 +24339,20 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>1488609</v>
+        <v>1488610</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Riasat Ali</t>
+          <t>Subhash</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>RPI(A)</t>
+          <t>MKD</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>16115</v>
+        <v>16105</v>
       </c>
       <c r="E386" t="n">
         <v>44</v>
@@ -24376,12 +24376,12 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>Riasat Ali</t>
+          <t>Subhash</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>RPI(A)</t>
+          <t>MKD</t>
         </is>
       </c>
       <c r="Q386" t="b">
@@ -32771,11 +32771,11 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>1489297</v>
+        <v>1489296</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Ramsharan Bhatt</t>
+          <t>Mohd. Mursaleen Qureshi</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -32808,7 +32808,7 @@
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>Ramsharan Bhatt</t>
+          <t>Mohd. Mursaleen Qureshi</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -32833,11 +32833,11 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>1489296</v>
+        <v>1489297</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Mohd. Mursaleen Qureshi</t>
+          <t>Ramsharan Bhatt</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>Mohd. Mursaleen Qureshi</t>
+          <t>Ramsharan Bhatt</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
@@ -33019,11 +33019,11 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>1489301</v>
+        <v>1489300</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Kulveer Singh</t>
+          <t>V.K.Kampani</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -33056,7 +33056,7 @@
       </c>
       <c r="K526" t="inlineStr">
         <is>
-          <t>Kulveer Singh</t>
+          <t>V.K.Kampani</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
@@ -33081,11 +33081,11 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>1489300</v>
+        <v>1489301</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>V.K.Kampani</t>
+          <t>Kulveer Singh</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -33118,7 +33118,7 @@
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>V.K.Kampani</t>
+          <t>Kulveer Singh</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -34197,11 +34197,11 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>1489399</v>
+        <v>1489400</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Mohd. Mursaleen Qureshi</t>
+          <t>Ramsharan Bhatt</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -34234,7 +34234,7 @@
       </c>
       <c r="K545" t="inlineStr">
         <is>
-          <t>Mohd. Mursaleen Qureshi</t>
+          <t>Ramsharan Bhatt</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
@@ -34259,11 +34259,11 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>1489400</v>
+        <v>1489399</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Ramsharan Bhatt</t>
+          <t>Mohd. Mursaleen Qureshi</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="K546" t="inlineStr">
         <is>
-          <t>Ramsharan Bhatt</t>
+          <t>Mohd. Mursaleen Qureshi</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
@@ -34445,11 +34445,11 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>1489403</v>
+        <v>1489404</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Abbas</t>
+          <t>Natthu Ram</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -34482,7 +34482,7 @@
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t>Abbas</t>
+          <t>Natthu Ram</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
@@ -34507,11 +34507,11 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>1489404</v>
+        <v>1489403</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Natthu Ram</t>
+          <t>Abbas</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -34544,7 +34544,7 @@
       </c>
       <c r="K550" t="inlineStr">
         <is>
-          <t>Natthu Ram</t>
+          <t>Abbas</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
@@ -36491,20 +36491,20 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>1489589</v>
+        <v>1489588</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Asif Khan</t>
+          <t>Sanjay</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D582" t="n">
-        <v>16068</v>
+        <v>16059</v>
       </c>
       <c r="E582" t="n">
         <v>175</v>
@@ -36528,12 +36528,12 @@
       </c>
       <c r="K582" t="inlineStr">
         <is>
-          <t>Asif Khan</t>
+          <t>Sanjay</t>
         </is>
       </c>
       <c r="L582" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q582" t="b">
@@ -36553,20 +36553,20 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>1489588</v>
+        <v>1489589</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Sanjay</t>
+          <t>Asif Khan</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="D583" t="n">
-        <v>16059</v>
+        <v>16068</v>
       </c>
       <c r="E583" t="n">
         <v>175</v>
@@ -36590,12 +36590,12 @@
       </c>
       <c r="K583" t="inlineStr">
         <is>
-          <t>Sanjay</t>
+          <t>Asif Khan</t>
         </is>
       </c>
       <c r="L583" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="Q583" t="b">
@@ -38475,20 +38475,20 @@
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>1489692</v>
+        <v>1489693</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Natthu Ram</t>
+          <t>Subhash</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MKD</t>
         </is>
       </c>
       <c r="D614" t="n">
-        <v>16059</v>
+        <v>16105</v>
       </c>
       <c r="E614" t="n">
         <v>53</v>
@@ -38512,12 +38512,12 @@
       </c>
       <c r="K614" t="inlineStr">
         <is>
-          <t>Natthu Ram</t>
+          <t>Subhash</t>
         </is>
       </c>
       <c r="L614" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MKD</t>
         </is>
       </c>
       <c r="Q614" t="b">
@@ -38537,20 +38537,20 @@
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>1489693</v>
+        <v>1489692</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Subhash</t>
+          <t>Natthu Ram</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>MKD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D615" t="n">
-        <v>16105</v>
+        <v>16059</v>
       </c>
       <c r="E615" t="n">
         <v>53</v>
@@ -38574,12 +38574,12 @@
       </c>
       <c r="K615" t="inlineStr">
         <is>
-          <t>Subhash</t>
+          <t>Natthu Ram</t>
         </is>
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t>MKD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q615" t="b">
@@ -38599,20 +38599,20 @@
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>1489695</v>
+        <v>1489694</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Ajay Kathuria</t>
+          <t>Riasat Ali</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RPI(A)</t>
         </is>
       </c>
       <c r="D616" t="n">
-        <v>16059</v>
+        <v>16115</v>
       </c>
       <c r="E616" t="n">
         <v>47</v>
@@ -38636,12 +38636,12 @@
       </c>
       <c r="K616" t="inlineStr">
         <is>
-          <t>Ajay Kathuria</t>
+          <t>Riasat Ali</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RPI(A)</t>
         </is>
       </c>
       <c r="Q616" t="b">
@@ -38661,20 +38661,20 @@
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>1489694</v>
+        <v>1489695</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Riasat Ali</t>
+          <t>Ajay Kathuria</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>RPI(A)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D617" t="n">
-        <v>16115</v>
+        <v>16059</v>
       </c>
       <c r="E617" t="n">
         <v>47</v>
@@ -38698,12 +38698,12 @@
       </c>
       <c r="K617" t="inlineStr">
         <is>
-          <t>Riasat Ali</t>
+          <t>Ajay Kathuria</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>RPI(A)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q617" t="b">
@@ -53587,7 +53587,7 @@
         </is>
       </c>
       <c r="Q857" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R857" t="n">
         <v>6</v>
@@ -53649,7 +53649,7 @@
         </is>
       </c>
       <c r="Q858" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R858" t="n">
         <v>6</v>
@@ -54455,7 +54455,7 @@
         </is>
       </c>
       <c r="Q871" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R871" t="n">
         <v>6</v>
@@ -54517,7 +54517,7 @@
         </is>
       </c>
       <c r="Q872" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R872" t="n">
         <v>6</v>
@@ -55323,7 +55323,7 @@
         </is>
       </c>
       <c r="Q885" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R885" t="n">
         <v>6</v>
@@ -55385,7 +55385,7 @@
         </is>
       </c>
       <c r="Q886" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R886" t="n">
         <v>6</v>
@@ -56191,7 +56191,7 @@
         </is>
       </c>
       <c r="Q899" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R899" t="n">
         <v>6</v>
@@ -56253,7 +56253,7 @@
         </is>
       </c>
       <c r="Q900" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R900" t="n">
         <v>6</v>
@@ -57059,7 +57059,7 @@
         </is>
       </c>
       <c r="Q913" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R913" t="n">
         <v>6</v>
@@ -57121,7 +57121,7 @@
         </is>
       </c>
       <c r="Q914" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R914" t="n">
         <v>6</v>
@@ -58733,7 +58733,7 @@
         </is>
       </c>
       <c r="Q940" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R940" t="n">
         <v>6</v>
@@ -58795,7 +58795,7 @@
         </is>
       </c>
       <c r="Q941" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R941" t="n">
         <v>6</v>
@@ -59601,7 +59601,7 @@
         </is>
       </c>
       <c r="Q954" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R954" t="n">
         <v>6</v>
@@ -59663,7 +59663,7 @@
         </is>
       </c>
       <c r="Q955" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R955" t="n">
         <v>6</v>
@@ -60469,7 +60469,7 @@
         </is>
       </c>
       <c r="Q968" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R968" t="n">
         <v>6</v>
@@ -60531,7 +60531,7 @@
         </is>
       </c>
       <c r="Q969" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R969" t="n">
         <v>6</v>
@@ -61337,7 +61337,7 @@
         </is>
       </c>
       <c r="Q982" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R982" t="n">
         <v>6</v>
@@ -61399,7 +61399,7 @@
         </is>
       </c>
       <c r="Q983" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R983" t="n">
         <v>6</v>
@@ -62205,7 +62205,7 @@
         </is>
       </c>
       <c r="Q996" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R996" t="n">
         <v>6</v>
@@ -62267,7 +62267,7 @@
         </is>
       </c>
       <c r="Q997" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R997" t="n">
         <v>6</v>
@@ -63073,7 +63073,7 @@
         </is>
       </c>
       <c r="Q1010" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R1010" t="n">
         <v>6</v>
@@ -63135,7 +63135,7 @@
         </is>
       </c>
       <c r="Q1011" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R1011" t="n">
         <v>6</v>
@@ -63941,7 +63941,7 @@
         </is>
       </c>
       <c r="Q1024" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R1024" t="n">
         <v>6</v>
@@ -64003,7 +64003,7 @@
         </is>
       </c>
       <c r="Q1025" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R1025" t="n">
         <v>6</v>
@@ -64809,7 +64809,7 @@
         </is>
       </c>
       <c r="Q1038" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R1038" t="n">
         <v>6</v>
@@ -64871,7 +64871,7 @@
         </is>
       </c>
       <c r="Q1039" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R1039" t="n">
         <v>6</v>
@@ -65677,7 +65677,7 @@
         </is>
       </c>
       <c r="Q1052" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R1052" t="n">
         <v>6</v>
@@ -65801,7 +65801,7 @@
         </is>
       </c>
       <c r="Q1054" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R1054" t="n">
         <v>6</v>

--- a/static/data/exports/Retro_UK_GE_2009.xlsx
+++ b/static/data/exports/Retro_UK_GE_2009.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -15845,20 +15845,20 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1487923</v>
+        <v>1487922</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Anjana Walia</t>
+          <t>Dr. Nagendra Dutt Jagoodi</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>RJSD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>16067</v>
+        <v>16059</v>
       </c>
       <c r="E249" t="n">
         <v>91</v>
@@ -15882,12 +15882,12 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Anjana Walia</t>
+          <t>Dr. Nagendra Dutt Jagoodi</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>RJSD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q249" t="b">
@@ -15907,20 +15907,20 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1487922</v>
+        <v>1487923</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Dr. Nagendra Dutt Jagoodi</t>
+          <t>Anjana Walia</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RJSD</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>16059</v>
+        <v>16067</v>
       </c>
       <c r="E250" t="n">
         <v>91</v>
@@ -15944,12 +15944,12 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Dr. Nagendra Dutt Jagoodi</t>
+          <t>Anjana Walia</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RJSD</t>
         </is>
       </c>
       <c r="Q250" t="b">
@@ -16412,7 +16412,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -16651,11 +16651,11 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1488010</v>
+        <v>1488011</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Barhm Dev Jha</t>
+          <t>Harish Walia</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Barhm Dev Jha</t>
+          <t>Harish Walia</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -16713,11 +16713,11 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1488011</v>
+        <v>1488010</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Harish Walia</t>
+          <t>Barhm Dev Jha</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Harish Walia</t>
+          <t>Barhm Dev Jha</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -17147,20 +17147,20 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1488018</v>
+        <v>1488019</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Bano Rani</t>
+          <t>Sunder Lal Thapliyal</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>NLHP</t>
+          <t>VVS</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>16071</v>
+        <v>16069</v>
       </c>
       <c r="E270" t="n">
         <v>85</v>
@@ -17184,12 +17184,12 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Bano Rani</t>
+          <t>Sunder Lal Thapliyal</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>NLHP</t>
+          <t>VVS</t>
         </is>
       </c>
       <c r="Q270" t="b">
@@ -17209,20 +17209,20 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1488019</v>
+        <v>1488018</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Sunder Lal Thapliyal</t>
+          <t>Bano Rani</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>VVS</t>
+          <t>NLHP</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>16069</v>
+        <v>16071</v>
       </c>
       <c r="E271" t="n">
         <v>85</v>
@@ -17246,12 +17246,12 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Sunder Lal Thapliyal</t>
+          <t>Bano Rani</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>VVS</t>
+          <t>NLHP</t>
         </is>
       </c>
       <c r="Q271" t="b">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -20070,7 +20070,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D317" t="n">
@@ -20495,20 +20495,20 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>1488346</v>
+        <v>1488345</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Anjana Walia</t>
+          <t>Dr. Nagendra Dutt Jagoodi</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>RJSD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>16067</v>
+        <v>16059</v>
       </c>
       <c r="E324" t="n">
         <v>43</v>
@@ -20532,12 +20532,12 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Anjana Walia</t>
+          <t>Dr. Nagendra Dutt Jagoodi</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>RJSD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q324" t="b">
@@ -20557,20 +20557,20 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>1488345</v>
+        <v>1488346</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Dr. Nagendra Dutt Jagoodi</t>
+          <t>Anjana Walia</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RJSD</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>16059</v>
+        <v>16067</v>
       </c>
       <c r="E325" t="n">
         <v>43</v>
@@ -20594,12 +20594,12 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Dr. Nagendra Dutt Jagoodi</t>
+          <t>Anjana Walia</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RJSD</t>
         </is>
       </c>
       <c r="Q325" t="b">
@@ -21124,7 +21124,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D334" t="n">
@@ -21301,11 +21301,11 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>1488419</v>
+        <v>1488420</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Harish Walia</t>
+          <t>Barhm Dev Jha</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Harish Walia</t>
+          <t>Barhm Dev Jha</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -21363,11 +21363,11 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>1488420</v>
+        <v>1488419</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Barhm Dev Jha</t>
+          <t>Harish Walia</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21400,7 +21400,7 @@
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Barhm Dev Jha</t>
+          <t>Harish Walia</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -22240,7 +22240,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -24277,20 +24277,20 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>1488609</v>
+        <v>1488610</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Riasat Ali</t>
+          <t>Subhash</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>RPI(A)</t>
+          <t>MKD</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>16115</v>
+        <v>16105</v>
       </c>
       <c r="E385" t="n">
         <v>44</v>
@@ -24314,12 +24314,12 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Riasat Ali</t>
+          <t>Subhash</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>RPI(A)</t>
+          <t>MKD</t>
         </is>
       </c>
       <c r="Q385" t="b">
@@ -24339,20 +24339,20 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>1488610</v>
+        <v>1488609</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Subhash</t>
+          <t>Riasat Ali</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>MKD</t>
+          <t>RPI(A)</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>16105</v>
+        <v>16115</v>
       </c>
       <c r="E386" t="n">
         <v>44</v>
@@ -24376,12 +24376,12 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>Subhash</t>
+          <t>Riasat Ali</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>MKD</t>
+          <t>RPI(A)</t>
         </is>
       </c>
       <c r="Q386" t="b">
@@ -32771,11 +32771,11 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>1489296</v>
+        <v>1489297</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Mohd. Mursaleen Qureshi</t>
+          <t>Ramsharan Bhatt</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -32808,7 +32808,7 @@
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>Mohd. Mursaleen Qureshi</t>
+          <t>Ramsharan Bhatt</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -32833,11 +32833,11 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>1489297</v>
+        <v>1489296</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Ramsharan Bhatt</t>
+          <t>Mohd. Mursaleen Qureshi</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>Ramsharan Bhatt</t>
+          <t>Mohd. Mursaleen Qureshi</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
@@ -38599,20 +38599,20 @@
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>1489694</v>
+        <v>1489695</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Riasat Ali</t>
+          <t>Ajay Kathuria</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>RPI(A)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D616" t="n">
-        <v>16115</v>
+        <v>16059</v>
       </c>
       <c r="E616" t="n">
         <v>47</v>
@@ -38636,12 +38636,12 @@
       </c>
       <c r="K616" t="inlineStr">
         <is>
-          <t>Riasat Ali</t>
+          <t>Ajay Kathuria</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t>RPI(A)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q616" t="b">
@@ -38661,20 +38661,20 @@
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>1489695</v>
+        <v>1489694</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Ajay Kathuria</t>
+          <t>Riasat Ali</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RPI(A)</t>
         </is>
       </c>
       <c r="D617" t="n">
-        <v>16059</v>
+        <v>16115</v>
       </c>
       <c r="E617" t="n">
         <v>47</v>
@@ -38698,12 +38698,12 @@
       </c>
       <c r="K617" t="inlineStr">
         <is>
-          <t>Ajay Kathuria</t>
+          <t>Riasat Ali</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RPI(A)</t>
         </is>
       </c>
       <c r="Q617" t="b">
@@ -53293,20 +53293,20 @@
     </row>
     <row r="853">
       <c r="A853" t="n">
-        <v>1490915</v>
+        <v>1490916</v>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Sushama</t>
+          <t>Kiran Arya</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D853" t="n">
-        <v>16088</v>
+        <v>16059</v>
       </c>
       <c r="E853" t="n">
         <v>196</v>
@@ -53330,12 +53330,12 @@
       </c>
       <c r="K853" t="inlineStr">
         <is>
-          <t>Sushama</t>
+          <t>Kiran Arya</t>
         </is>
       </c>
       <c r="L853" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q853" t="b">
@@ -53355,20 +53355,20 @@
     </row>
     <row r="854">
       <c r="A854" t="n">
-        <v>1490916</v>
+        <v>1490915</v>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Kiran Arya</t>
+          <t>Sushama</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="D854" t="n">
-        <v>16059</v>
+        <v>16088</v>
       </c>
       <c r="E854" t="n">
         <v>196</v>
@@ -53392,12 +53392,12 @@
       </c>
       <c r="K854" t="inlineStr">
         <is>
-          <t>Kiran Arya</t>
+          <t>Sushama</t>
         </is>
       </c>
       <c r="L854" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="Q854" t="b">
